--- a/exam_schedule.xlsx
+++ b/exam_schedule.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>DS3004</t>
+          <t>EE1005</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Data Warehousing and Business Intellligence</t>
+          <t>Digital Logic Design</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>MG3040</t>
+          <t>CS3014</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Methods in Business Research</t>
+          <t>Applied Human Computer Interaction</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>MG3040</t>
+          <t>SE4009</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Methods in Business Research</t>
+          <t>Process Mining and Simulation\</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -797,27 +797,27 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>SE4009</t>
+          <t>EE2003</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Process Mining and Simulation\</t>
+          <t>Computer Organization and Assembly Language</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -937,27 +937,27 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>EE2003</t>
+          <t>NS1001</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Computer Organization and Assembly Language</t>
+          <t>Applied Physics</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(SE) (A,B,C,D,E)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D,E)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1007,27 +1007,27 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>NS1001</t>
+          <t>DS3003</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Applied Physics</t>
+          <t>Data Warehousing and Business Intellligence</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>DS3003</t>
+          <t>SS1012</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Data Warehousing and Business Intellligence</t>
+          <t>Functional English</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(SE) (A,B, C,D,E)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1217,27 +1217,27 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>SS1012</t>
+          <t>CS3014</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Functional English</t>
+          <t>Applied Human Computer Interaction</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1252,27 +1252,27 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>CS3014</t>
+          <t>EE2003</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Applied Human Computer Interaction</t>
+          <t>Computer Organization and Assembly Language</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>EE2003</t>
+          <t>DS3004</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Computer Organization and Assembly Language</t>
+          <t>Data Warehousing and Business Intellligence</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1427,17 +1427,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>CS4075</t>
+          <t>EE2003</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Computer Organization and Assembly Language</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1462,27 +1462,27 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>CS4075</t>
+          <t>EE2003</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Computer Organization and Assembly Language</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B)</t>
+          <t>BS(AI) (A)</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1497,27 +1497,27 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>CS3014</t>
+          <t>CS4075</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Applied Human Computer Interaction</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(CS) (A,B)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1532,27 +1532,27 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>EE2003</t>
+          <t>CS4075</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Computer Organization and Assembly Language</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B)</t>
+          <t>BS(CY) (A,B)</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1567,22 +1567,22 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>EE2003</t>
+          <t>AI2002</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Computer Organization and Assembly Language</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A)</t>
+          <t>BS(SE) (A,B,C)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>AI3001</t>
+          <t>AI2002</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Knowledge Rep. and Reasoning</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -1707,27 +1707,27 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>AI2002</t>
+          <t>MG3040</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Methods in Business Research</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1742,27 +1742,27 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>AI2002</t>
+          <t>MG3040</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Methods in Business Research</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>26-09-21</t>
+          <t>26-09-19</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1782,17 +1782,17 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>SS2012</t>
+          <t>AI3001</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Technical and Business Writing</t>
+          <t>Knowledge Rep. and Reasoning</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B, C)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -1917,27 +1917,27 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>SS2012</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Technical and Business Writing</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -2092,27 +2092,27 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>CS3004</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Software Design and Analysis</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>SS1015</t>
+          <t>CS3004</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Pakistan Studies</t>
+          <t>Software Design and Analysis</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>EE3009</t>
+          <t>SS1015</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Computer Architecture</t>
+          <t>Pakistan Studies</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -2267,27 +2267,27 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>SS1021</t>
+          <t>EE3009</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Understanding of Holy Quran I/Introduction to Major World Religions I</t>
+          <t>Computer Architecture</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -2337,27 +2337,27 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>5:00 to 6:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>CS3002</t>
+          <t>SS1021</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Information Security</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions I</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -2757,27 +2757,27 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>AI4015</t>
+          <t>CS4049</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Agentic Artificial Intelligenc</t>
+          <t>Blockchain and Cryptocurrency</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(CY) (A,B)</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -2792,22 +2792,22 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>AI4015</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Agentic Artificial Intelligenc</t>
+          <t>Technical and Business Writing</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>AI4015</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Agentic Artificial Intelligenc</t>
+          <t>Technical and Business Writing</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>SS1021</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Understanding of Holy Quran I/Introduction to Major World Religions I</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -2897,22 +2897,22 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>SS1021</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Understanding of Holy Quran I/Introduction to Major World Religions I</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -2932,27 +2932,27 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>5:00 to 6:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>CS3002</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Information Security</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,,E,F,G)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -2967,27 +2967,27 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>5:00 to 6:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>CS3002</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Information Security</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -3002,27 +3002,27 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Technical and Business Writing</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>CS4046</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Technical and Business Writing</t>
+          <t>Game Design and Development</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3072,27 +3072,27 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>AI4015</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Agentic Artificial Intelligenc</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3107,27 +3107,27 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>AI4015</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Agentic Artificial Intelligenc</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3142,27 +3142,27 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>AI4015</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Agentic Artificial Intelligenc</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3177,27 +3177,27 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>CS3002</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Information Security</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3217,22 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>CS1004</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Object Oriented Programming</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(CS) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3247,27 +3247,27 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>CS4046</t>
+          <t>CS1004</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Game Design and Development</t>
+          <t>Object Oriented Programming</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(SE) (A)</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3282,27 +3282,27 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>AI4015</t>
+          <t>CS1004</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Agentic Artificial Intelligenc</t>
+          <t>Object Oriented Programming</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(AI) (A)</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -3387,27 +3387,27 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>CS4049</t>
+          <t>AI4015</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Blockchain and Cryptocurrency</t>
+          <t>Agentic Artificial Intelligenc</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3422,27 +3422,27 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>CS2005</t>
+          <t>CS3002</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Database Systems</t>
+          <t>Information Security</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,,E,F,G)</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>CY3003</t>
+          <t>CS3002</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Information Assurance</t>
+          <t>Information Security</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>BS(CY)</t>
+          <t>BS(SE) (A,B)</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -3497,22 +3497,22 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>CS1004</t>
+          <t>CS4059</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Object Oriented Programming</t>
+          <t>Fundamentals of Computer Vision</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3527,27 +3527,27 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>CS1004</t>
+          <t>CY3003</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Object Oriented Programming</t>
+          <t>Information Assurance</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A)</t>
+          <t>BS(CY)</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3557,32 +3557,32 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>26-09-21</t>
+          <t>26-09-22</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>CS1004</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Object Oriented Programming</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -3592,32 +3592,32 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>26-09-21</t>
+          <t>26-09-22</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>CS4059</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Computer Vision</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(SE) (A,B, C,D,E)</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -3737,27 +3737,27 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>AI3002</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -3772,22 +3772,22 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>SS1007</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>Islamic Studies/Ethics</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -3807,27 +3807,27 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>EE1005</t>
+          <t>SS1007</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Digital Logic Design</t>
+          <t>Islamic Studies/Ethics</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(AI) (A,B, C)</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -3877,27 +3877,27 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>SS1007</t>
+          <t>CS2001</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Islamic Studies/Ethics</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B, C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3912,27 +3912,27 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>SS1007</t>
+          <t>CS2001</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Islamic Studies/Ethics</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -4052,27 +4052,27 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>CS2001</t>
+          <t>CS2009</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Design and Analysis of Algorithms</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -4087,27 +4087,27 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>CS2001</t>
+          <t>CS2009</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Design and Analysis of Algorithms</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(SE) (A,B,C)</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -4192,27 +4192,27 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>CS2009</t>
+          <t>CS1005</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Design and Analysis of Algorithms</t>
+          <t>Discrete Structures</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS) (A,B)</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -4227,27 +4227,27 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>CS2009</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Design and Analysis of Algorithms</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -4262,27 +4262,27 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>CS1005</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Discrete Structures</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B)</t>
+          <t>BS(SE) (A,B, C,D,E)</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -4402,27 +4402,27 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>CS4001</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>Professional Practices in IT</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,,E,F,G,H)</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -4437,27 +4437,27 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>CS4001</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>Professional Practices in IT</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(CY) (A,B)</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -4472,27 +4472,27 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>EE1005</t>
+          <t>SS1007</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Digital Logic Design</t>
+          <t>Islamic Studies/Ethics</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
+          <t>BS(AI) (A,B, C)</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B, C)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -4577,27 +4577,27 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>SS1007</t>
+          <t>CS2001</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Islamic Studies/Ethics</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -4752,27 +4752,27 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>CS2001</t>
+          <t>CS2009</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Design and Analysis of Algorithms</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(SE) (A,B,C)</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -4892,27 +4892,27 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>CS2009</t>
+          <t>CS4039</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Design and Analysis of Algorithms</t>
+          <t>Software for Mobile Devices</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -4962,27 +4962,27 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>CS4039</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Software for Mobile Devices</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(SE) (A,B, C,D,E)</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -5137,27 +5137,27 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>CS4032</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>Web Programming</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(CY)</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -5172,27 +5172,27 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>CS4001</t>
+          <t>CS2001</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Professional Practices in IT</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,,E,F,G,H)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -5207,27 +5207,27 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>CS4001</t>
+          <t>CS2001</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Professional Practices in IT</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -5242,27 +5242,27 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>CS4032</t>
+          <t>CS2001</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Web Programming</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>BS(CY)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -5347,27 +5347,27 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>CS2001</t>
+          <t>CS4044</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Fundamentals of Software Project Management</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -5382,27 +5382,27 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>CS2001</t>
+          <t>CS2005</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Database Systems</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -5417,22 +5417,22 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>CS2001</t>
+          <t>CY2004</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(CY)</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -5452,22 +5452,22 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>CS4044</t>
+          <t>AI4012</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Software Project Management</t>
+          <t>Multiagent Systems and Game Theory</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>AI3002</t>
+          <t>AI4012</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Multiagent Systems and Game Theory</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -5522,27 +5522,27 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>CY2004</t>
+          <t>CS4085</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>BS(CY)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -5557,27 +5557,27 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>AI4012</t>
+          <t>DS2003</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Multiagent Systems and Game Theory</t>
+          <t>Advanced Statistics</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -5592,22 +5592,22 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>AI4012</t>
+          <t>CS4063</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Multiagent Systems and Game Theory</t>
+          <t>Natural Language Processing</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(SE) (A,B)</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>CS4085</t>
+          <t>SE3005</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Software Construction and Development</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(SE) (A,B,C)</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -5657,32 +5657,32 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>26-09-22</t>
+          <t>26-09-23</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>DS2003</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Advanced Statistics</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -5692,32 +5692,32 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>26-09-22</t>
+          <t>26-09-23</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>CS4063</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -5727,32 +5727,32 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>26-09-22</t>
+          <t>26-09-23</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>SE3005</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Software Construction and Development</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -5837,27 +5837,27 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>CY4054</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Blockchain Technologies and Applications</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -5872,27 +5872,27 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -5907,27 +5907,27 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -5942,27 +5942,27 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>CY4054</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Blockchain Technologies and Applications</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -6047,27 +6047,27 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>CS4045</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Deep Learning for Perception</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -6082,27 +6082,27 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>CS3001</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -6117,27 +6117,27 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>CS3001</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -6152,27 +6152,27 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>CS4045</t>
+          <t>DS2001</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Deep Learning for Perception</t>
+          <t>Introduction to Data Science</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6187,27 +6187,27 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>CS3001</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6222,27 +6222,27 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>CS3001</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6257,27 +6257,27 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>DS2001</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Data Science</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -6362,27 +6362,27 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6397,27 +6397,27 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6432,27 +6432,27 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -6537,27 +6537,27 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>AI4019</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Edge Computing and Intelligent Systems</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(AI) (A,B)</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -6572,27 +6572,27 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>AI4019</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Edge Computing and Intelligent Systems</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(DS) (A)</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -6607,27 +6607,27 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>CS3001</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -6642,27 +6642,27 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>AI4019</t>
+          <t>SE1001</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Edge Computing and Intelligent Systems</t>
+          <t>Introduction to Software Engineering</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6677,22 +6677,22 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>AI4019</t>
+          <t>SE4033</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Edge Computing and Intelligent Systems</t>
+          <t>Formal Methods in Software Engineering</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -6712,27 +6712,27 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>CS3001</t>
+          <t>SS0000</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Arts and Humanities</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6747,27 +6747,27 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>SE1001</t>
+          <t>SS0000</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Software Engineering</t>
+          <t>Arts and Humanities</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6782,22 +6782,22 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>SE4033</t>
+          <t>CY4048</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Formal Methods in Software Engineering</t>
+          <t>Security Operations and Administration</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(CY) (A,B)</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -6817,27 +6817,27 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>SS0000</t>
+          <t>CY4048</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>Arts and Humanities</t>
+          <t>Security Operations and Administration</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(CY) (A)</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -6852,27 +6852,27 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>SS0000</t>
+          <t>AI2001</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Arts and Humanities</t>
+          <t>Programming for AI</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>CY4048</t>
+          <t>CS2006</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Security Operations and Administration</t>
+          <t>Operating Systems</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -6922,27 +6922,27 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>CY4048</t>
+          <t>CS2006</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Security Operations and Administration</t>
+          <t>Operating Systems</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A)</t>
+          <t>BS(DS) (A)</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -6957,27 +6957,27 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>AI2001</t>
+          <t>CS4095</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Programming for AI</t>
+          <t>Embedded Control of Robotics</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -6992,27 +6992,27 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>CS2006</t>
+          <t>SS0000</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>Operating Systems</t>
+          <t>Arts and Humanities</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -7027,27 +7027,27 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>CS2006</t>
+          <t>SS0000</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>Operating Systems</t>
+          <t>Arts and Humanities</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -7062,22 +7062,22 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>CS4095</t>
+          <t>AI4013</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Embedded Control of Robotics</t>
+          <t>AI Product Development</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -7097,27 +7097,27 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>SS0000</t>
+          <t>CS3006</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>Arts and Humanities</t>
+          <t>Parallel and Distributed Computing</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(CS) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7132,27 +7132,27 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>SS0000</t>
+          <t>CS3006</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Arts and Humanities</t>
+          <t>Parallel and Distributed Computing</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(SE) (A,B)</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7167,22 +7167,22 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>AI4013</t>
+          <t>CS3012</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>AI Product Development</t>
+          <t>Fundamentals of Data Visualization</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -7207,125 +7207,20 @@
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>CS3006</t>
+          <t>SE3002</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>Parallel and Distributed Computing</t>
+          <t>Software Quality Engineering</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D)</t>
+          <t>BS(SE) (A,B,C)</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="3" t="n">
-        <v>193</v>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>26-09-23</t>
-        </is>
-      </c>
-      <c r="C196" s="3" t="inlineStr">
-        <is>
-          <t>03:40 to 04:40 PM</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>CS3006</t>
-        </is>
-      </c>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>Parallel and Distributed Computing</t>
-        </is>
-      </c>
-      <c r="F196" s="4" t="inlineStr">
-        <is>
-          <t>BS(SE) (A,B)</t>
-        </is>
-      </c>
-      <c r="G196" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>26-09-23</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="inlineStr">
-        <is>
-          <t>9:00 to 10:00 AM</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>CS3012</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>Fundamentals of Data Visualization</t>
-        </is>
-      </c>
-      <c r="F197" s="4" t="inlineStr">
-        <is>
-          <t>BS(CS)</t>
-        </is>
-      </c>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>26-09-23</t>
-        </is>
-      </c>
-      <c r="C198" s="3" t="inlineStr">
-        <is>
-          <t>03:40 to 04:40 PM</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>SE3002</t>
-        </is>
-      </c>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>Software Quality Engineering</t>
-        </is>
-      </c>
-      <c r="F198" s="4" t="inlineStr">
-        <is>
-          <t>BS(SE) (A,B,C)</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -7345,7 +7240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7907,17 +7802,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>MG4066</t>
+          <t>AF4016</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Managing Virtual Global Teams</t>
+          <t>Applied Financial Management</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -8222,22 +8117,22 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>SS1018</t>
+          <t>MG4067</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Understanding Holy Quran</t>
+          <t>Strategic Diversity, Equity and Inclusion</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -8357,27 +8252,27 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>MG4067</t>
+          <t>SS2019</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Strategic Diversity, Equity and Inclusion</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -8392,17 +8287,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>SS2019</t>
+          <t>MG3012</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Blockchain Technology for Business</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -8412,7 +8307,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -8427,17 +8322,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>5:00 to 6:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>AF4016</t>
+          <t>AF4006</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Applied Financial Management</t>
+          <t>Investment Anal. and Mgmt.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -8462,17 +8357,17 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>MG3012</t>
+          <t>SS2019</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Blockchain Technology for Business</t>
+          <t>Psychology</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -8497,22 +8392,22 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>AF4006</t>
+          <t>BA4009</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Investment Anal. and Mgmt.</t>
+          <t>Design Thinking in Business Analytics</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -8527,32 +8422,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>26-09-19</t>
+          <t>26-09-21</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>SS2019</t>
+          <t>SS2042</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Community Service</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -8562,32 +8457,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>26-09-19</t>
+          <t>26-09-21</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>BA4009</t>
+          <t>MG1011</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Design Thinking in Business Analytics</t>
+          <t>Business Mathematics</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -8602,27 +8497,27 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>SS2042</t>
+          <t>MG1011</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Community Service</t>
+          <t>Business Mathematics</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8547,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -8672,17 +8567,17 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>MG1011</t>
+          <t>MG4011</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Business Mathematics</t>
+          <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -8692,7 +8587,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -8707,17 +8602,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>MG1011</t>
+          <t>MG1001</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Business Mathematics</t>
+          <t>Fundamentals of Management</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -8742,27 +8637,27 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>MG4011</t>
+          <t>MG1001</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Entrepreneurship</t>
+          <t>Fundamentals of Management</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -8777,17 +8672,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>MG1001</t>
+          <t>MG2003</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Management</t>
+          <t>Consumer Behaviour</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -8797,7 +8692,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -8812,17 +8707,17 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>MG1001</t>
+          <t>MG2003</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Management</t>
+          <t>Consumer Behaviour</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -8832,7 +8727,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -8847,27 +8742,27 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>MG2003</t>
+          <t>MG4523</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Consumer Behaviour</t>
+          <t>Conflict Resolution and Negotiation Skills</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -8882,27 +8777,27 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>5:00 to 6:00 PM</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>MG2003</t>
+          <t>BA4006</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Consumer Behaviour</t>
+          <t>Contextual Marketing and Product Analytics</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -8917,27 +8812,27 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>MG4523</t>
+          <t>SS2043</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Conflict Resolution and Negotiation Skills</t>
+          <t>Civics and Community Engagement</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -8952,22 +8847,22 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>5:00 to 6:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>MT2004</t>
+          <t>SS2043</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Business Math – II</t>
+          <t>Civics and Community Engagement</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -8987,27 +8882,27 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>SS2043</t>
+          <t>MG1011</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Civics and Community Engagement</t>
+          <t>Business Mathematics</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -9022,27 +8917,27 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>SS2043</t>
+          <t>MG1011</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Civics and Community Engagement</t>
+          <t>Business Mathematics</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -9072,7 +8967,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -9092,27 +8987,27 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>MG1011</t>
+          <t>MG4011</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Business Mathematics</t>
+          <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -9127,17 +9022,17 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>MG1011</t>
+          <t>MG4011</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Business Mathematics</t>
+          <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -9147,7 +9042,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -9162,22 +9057,22 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>MG4011</t>
+          <t>MG4062</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Entrepreneurship</t>
+          <t>Brand Management</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -9197,27 +9092,27 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>MG4011</t>
+          <t>SS2006</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Entrepreneurship</t>
+          <t>Macro Economics</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -9232,27 +9127,27 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>MG4062</t>
+          <t>MG2011</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Brand Management</t>
+          <t>Environmental Science and Sustainability for Business</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -9267,27 +9162,27 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>SS2006</t>
+          <t>MG2011</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Macro Economics</t>
+          <t>Environmental Science and Sustainability for Business</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -9302,27 +9197,27 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>5:00 to 6:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>MG1004</t>
+          <t>MT1002</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Business Calculus II</t>
+          <t>Business Math – I</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -9337,22 +9232,22 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>MG2011</t>
+          <t>MG2001</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Environmental Science and Sustainability for Business</t>
+          <t>Organizational Behaviour</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -9372,27 +9267,27 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>MG2011</t>
+          <t>AF4017</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Environmental Science and Sustainability for Business</t>
+          <t>Digital Assets and Cryptocurrencies; Conventiontional and Shariah Persepectives</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -9407,27 +9302,27 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>MG2001</t>
+          <t>MG3002</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Organizational Behaviour</t>
+          <t>Business Law</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -9442,27 +9337,27 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>MG3002</t>
+          <t>MT2004</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>Business Math – II</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -9477,27 +9372,27 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>5:00 to 6:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>BA4006</t>
+          <t>MG2011</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Contextual Marketing and Product Analytics</t>
+          <t>Environmental Science and Sustainability for Business</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -9527,7 +9422,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -9547,22 +9442,22 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>MG2011</t>
+          <t>AF2001</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Environmental Science and Sustainability for Business</t>
+          <t>Corporate Accounting – I</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -9582,27 +9477,27 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>AF2001</t>
+          <t>MG1004</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Corporate Accounting – I</t>
+          <t>Business Calculus II</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -9617,22 +9512,22 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>5:00 to 6:00 PM</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>AF4017</t>
+          <t>MG4066</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Digital Assets and Cryptocurrencies; Conventiontional and Shariah Persepectives</t>
+          <t>Managing Virtual Global Teams</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -10017,7 +9912,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -10287,22 +10182,22 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>MT1002</t>
+          <t>CY4053</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Business Math – I</t>
+          <t>Cybersecurity for FinTech</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -10462,22 +10357,22 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>CY4053</t>
+          <t>MG3006</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity for FinTech</t>
+          <t>Operations Management</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -10602,22 +10497,22 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>MG3006</t>
+          <t>AF4005</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Operations Management</t>
+          <t>Audit and Assurance</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -10672,22 +10567,22 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>MG3014</t>
+          <t>CS2012</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Advanced Business Communications</t>
+          <t>Introduction to Object-Oriented Programming</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10707,12 +10602,12 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>AF4005</t>
+          <t>MG2010</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Audit and Assurance</t>
+          <t>Business Communication</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -10722,7 +10617,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10737,27 +10632,27 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>CS2012</t>
+          <t>MG3014</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Object-Oriented Programming</t>
+          <t>Advanced Business Communications</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -10767,32 +10662,32 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>26-09-22</t>
+          <t>26-09-23</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>MG2010</t>
+          <t>CS1001</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Business Communication</t>
+          <t>IT in Business</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10717,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -10857,7 +10752,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -10877,27 +10772,27 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>CS1001</t>
+          <t>MG4522</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>IT in Business</t>
+          <t>Islamic Banking and Finance</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -10912,17 +10807,17 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>MG4522</t>
+          <t>MG2012</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Islamic Banking and Finance</t>
+          <t>Business Economics</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -10932,7 +10827,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10857,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -10997,7 +10892,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -11032,7 +10927,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -11052,27 +10947,27 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>MG2012</t>
+          <t>MG4045</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Business Economics</t>
+          <t>Strategic Business Reporting</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -11087,17 +10982,17 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>MG4045</t>
+          <t>MG1002</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Strategic Business Reporting</t>
+          <t>Marketing Management</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -11107,7 +11002,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11032,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -11157,27 +11052,27 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>MG1002</t>
+          <t>MG3003</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Marketing Management</t>
+          <t>Basic Econometrics</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11102,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -11242,7 +11137,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -11262,27 +11157,27 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>MG3003</t>
+          <t>CS1001</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Basic Econometrics</t>
+          <t>IT in Business</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11207,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -11347,7 +11242,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -11367,27 +11262,27 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>CS1001</t>
+          <t>SS2002</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>IT in Business</t>
+          <t>Micro Economics</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11402,27 +11297,27 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>SS2002</t>
+          <t>MG2012</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Micro Economics</t>
+          <t>Business Economics</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11347,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -11487,7 +11382,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -11522,7 +11417,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -11542,27 +11437,27 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>MG2012</t>
+          <t>AF2005</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Business Economics</t>
+          <t>Cost and Management Accounting</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11577,27 +11472,27 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>AF2005</t>
+          <t>SS2018</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Cost and Management Accounting</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -11612,27 +11507,27 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>SS2018</t>
+          <t>MG3003</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Basic Econometrics</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11557,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -11697,7 +11592,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -11717,17 +11612,17 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>MG3003</t>
+          <t>BA4007</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Basic Econometrics</t>
+          <t>Empowering Organizations with Analytics and Data Visualization</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -11737,7 +11632,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -11752,22 +11647,22 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>BA4007</t>
+          <t>AF4011</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Empowering Organizations with Analytics and Data Visualization</t>
+          <t>Investment and Portfolio Analytics</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -11787,27 +11682,27 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>AF4011</t>
+          <t>SS2018</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Investment and Portfolio Analytics</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11822,27 +11717,27 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>SS2018</t>
+          <t>MG4003</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Strategic Management</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BBA (A,B)</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -11857,27 +11752,27 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>MG4003</t>
+          <t>MG3004</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Strategic Management</t>
+          <t>Human Resource Mgmt.</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11802,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -11927,27 +11822,27 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>MG3004</t>
+          <t>MG4521</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Human Resource Mgmt.</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -11977,45 +11872,10 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>26-09-23</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>02:30 to 03:30 PM</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>MG4521</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>Digital Marketing</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>BBA (A)</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -12035,7 +11895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12347,17 +12207,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>EE2007</t>
+          <t>MT1001</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Data Communication and Networks</t>
+          <t>Applied Calculus</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -12367,7 +12227,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -12382,27 +12242,27 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>EE2007</t>
+          <t>MT1001</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Data Communication and Networks</t>
+          <t>Applied Calculus</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -12412,22 +12272,22 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>26-09-21</t>
+          <t>26-09-19</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>MG1008</t>
+          <t>EE2007</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Occupational Health and Safety</t>
+          <t>Data Communication and Networks</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -12437,7 +12297,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -12447,32 +12307,32 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>26-09-21</t>
+          <t>26-09-19</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>MG1008</t>
+          <t>EE2007</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Occupational Health and Safety</t>
+          <t>Data Communication and Networks</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -12482,27 +12342,27 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>26-09-21</t>
+          <t>26-09-19</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>EE3006</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Technical and Business Writing</t>
+          <t>Embedded Systems</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -12522,17 +12382,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>NS1002</t>
+          <t>MG1008</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Physics for Engineers</t>
+          <t>Occupational Health and Safety</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -12557,17 +12417,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>NS1002</t>
+          <t>MG1008</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Physics for Engineers</t>
+          <t>Occupational Health and Safety</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -12592,17 +12452,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>CS2021</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Object Oriented Data Structures</t>
+          <t>Technical and Business Writing</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -12612,7 +12472,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -12627,27 +12487,27 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>EE1004</t>
+          <t>CY4054</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Electronic Devices and Circuits</t>
+          <t>Blockchain Technologies and Applications</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -12662,17 +12522,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>EE3002</t>
+          <t>CS2021</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>µP Interfacing and Programming</t>
+          <t>Object Oriented Data Structures</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -12682,7 +12542,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -12697,27 +12557,27 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>MG1008</t>
+          <t>EE1004</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Occupational Health and Safety</t>
+          <t>Electronic Devices and Circuits</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(CE) (A,B)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -12732,27 +12592,27 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>MG1008</t>
+          <t>EE3002</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Occupational Health and Safety</t>
+          <t>µP Interfacing and Programming</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -12767,27 +12627,27 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>EE2004</t>
+          <t>MG1008</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Electrical Network Analysis</t>
+          <t>Occupational Health and Safety</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -12802,22 +12662,22 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>NS1002</t>
+          <t>MG1008</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Physics for Engineers</t>
+          <t>Occupational Health and Safety</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -12837,27 +12697,27 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>NS1002</t>
+          <t>EE2004</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Physics for Engineers</t>
+          <t>Electrical Network Analysis</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -12942,27 +12802,27 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>CY4054</t>
+          <t>CS1011</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Blockchain Technologies and Applications</t>
+          <t>Programming for Engineers</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -12982,12 +12842,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>CS1011</t>
+          <t>ME2002</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Programming for Engineers</t>
+          <t>Applied Thermodynamics</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -12997,7 +12857,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -13007,27 +12867,27 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>26-09-21</t>
+          <t>26-09-22</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>EE1001</t>
+          <t>MT2013</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Linear Circuit Analysis</t>
+          <t>Complex Variables and Transforms</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(CE) (A,B)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -13042,32 +12902,32 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>26-09-21</t>
+          <t>26-09-22</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>ME2002</t>
+          <t>MT2013</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Applied Thermodynamics</t>
+          <t>Complex Variables and Transforms</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13082,27 +12942,27 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>MT2013</t>
+          <t>EE2012</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Complex Variables and Transforms</t>
+          <t>Computer Organization and Architecture</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13117,27 +12977,27 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>MT2013</t>
+          <t>SS1005</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Complex Variables and Transforms</t>
+          <t>English Language</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13152,27 +13012,27 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>EE2012</t>
+          <t>SS1005</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Computer Organization and Architecture</t>
+          <t>English Language</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13187,27 +13047,27 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>SS1005</t>
+          <t>EE3005</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>English Language</t>
+          <t>Electromagnetic Theory</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13222,27 +13082,27 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>SS1005</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>English Language</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A,B)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13257,27 +13117,27 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>EE3005</t>
+          <t>NS1002</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Electromagnetic Theory</t>
+          <t>Physics for Engineers</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13292,27 +13152,27 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>NS1002</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Physics for Engineers</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A,B,C)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13327,27 +13187,27 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>EE3006</t>
+          <t>MT2011</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Embedded Systems</t>
+          <t>Complex Variables and Transforms</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13362,27 +13222,27 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>MT2011</t>
+          <t>NS1007</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Complex Variables and Transforms</t>
+          <t>Applied Physics</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13397,17 +13257,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>NS1007</t>
+          <t>EE2031</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Applied Physics</t>
+          <t>Instrumentation and Measurements</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -13417,7 +13277,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -13432,27 +13292,27 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>CS2011</t>
+          <t>EE3005</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Databases</t>
+          <t>Electromagnetic Theory</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13467,27 +13327,27 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>EE3005</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Electromagnetic Theory</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13502,27 +13362,27 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>MT1009</t>
+          <t>NS1002</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra and Diff. Equations</t>
+          <t>Physics for Engineers</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13537,27 +13397,27 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>MT2003</t>
+          <t>NS1002</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Complex Variables and Transforms</t>
+          <t>Physics for Engineers</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (B,C)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13572,22 +13432,22 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>EE2031</t>
+          <t>MT2003</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Instrumentation and Measurements</t>
+          <t>Complex Variables and Transforms</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(EE) (B,C)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -13602,32 +13462,32 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>26-09-23</t>
+          <t>26-09-22</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>CS1009</t>
+          <t>CS2011</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Applications of Information Communication Technologies</t>
+          <t>Fundamentals of Databases</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -13657,7 +13517,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -13677,27 +13537,27 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>CS1005</t>
+          <t>CS1009</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Discrete Structures</t>
+          <t>Applications of Information Communication Technologies</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A,B)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13712,27 +13572,27 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>ME2001</t>
+          <t>CS1005</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Basic Mechanical Engineering</t>
+          <t>Discrete Structures</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A,B)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13747,17 +13607,17 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>SS1021</t>
+          <t>ME2001</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Understanding of Holy Quran I/Introduction to Major World Religions I</t>
+          <t>Basic Mechanical Engineering</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -13767,7 +13627,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13782,17 +13642,17 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>EE3003</t>
+          <t>SS1021</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Analogue and Digital Communication</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions I</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -13802,7 +13662,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13817,27 +13677,27 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>SS1015</t>
+          <t>EE3003</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Pakistan Studies</t>
+          <t>Analogue and Digital Communication</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -13867,7 +13727,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -13887,22 +13747,22 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>CS1009</t>
+          <t>SS1015</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Applications of Information Communication Technologies</t>
+          <t>Pakistan Studies</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -13937,7 +13797,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -13957,27 +13817,27 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>AI4003</t>
+          <t>CS1009</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Applied Machine Learning</t>
+          <t>Applications of Information Communication Technologies</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13992,27 +13852,27 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>EE3031</t>
+          <t>AI4003</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Digital Signal Processing</t>
+          <t>Applied Machine Learning</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -14027,22 +13887,22 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>EE3010</t>
+          <t>EE3031</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Analogue and Digital Communication</t>
+          <t>Digital Signal Processing</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -14062,27 +13922,27 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>SS1015</t>
+          <t>EE3010</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Pakistan Studies</t>
+          <t>Analogue and Digital Communication</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -14112,7 +13972,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -14132,27 +13992,97 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
+          <t>03:40 to 04:40 PM</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>SS1015</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Pakistan Studies</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>BS(EE) (A,B,C)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>26-09-23</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
           <t>02:30 to 03:30 PM</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>CS2008</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>Numerical Computing</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>BS(CE) (A)</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>26-09-23</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>02:30 to 03:30 PM</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>EE1001</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Linear Circuit Analysis</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>BS(EE) (A)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
         </is>
       </c>
     </row>

--- a/exam_schedule.xlsx
+++ b/exam_schedule.xlsx
@@ -3257,7 +3257,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Agentic Artificial Intelligenc</t>
+          <t>Agentic Artificial Intelligence</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Agentic Artificial Intelligenc</t>
+          <t>Agentic Artificial Intelligence</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Agentic Artificial Intelligenc</t>
+          <t>Agentic Artificial Intelligence</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
     </row>

--- a/exam_schedule.xlsx
+++ b/exam_schedule.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Process Mining and Simulation\</t>
+          <t>Process Mining and Simulation</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1532,22 +1532,22 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>CS4075</t>
+          <t>MG3040</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Methods in Business Research</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -1567,22 +1567,22 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>CS4075</t>
+          <t>MG3040</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Methods in Business Research</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -1602,27 +1602,27 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>AI2002</t>
+          <t>CS4075</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C)</t>
+          <t>BS(CS) (A,B)</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1637,27 +1637,27 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>AI2002</t>
+          <t>CS4075</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(CY) (A,B)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1672,22 +1672,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>EL1005</t>
+          <t>CL2001</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Digital Logic Design Lab</t>
+          <t>Data Structures Lab</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -1707,27 +1707,27 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>AI4009</t>
+          <t>CL2001</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Generative AI</t>
+          <t>Data Structures Lab</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -1742,27 +1742,27 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>AI4009</t>
+          <t>AI2002</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Generative AI</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(SE) (A,B,C)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1777,27 +1777,27 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>MG3040</t>
+          <t>AI2002</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Methods in Business Research</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1812,27 +1812,27 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>MG3040</t>
+          <t>EL1005</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Methods in Business Research</t>
+          <t>Digital Logic Design Lab</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -1847,27 +1847,27 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>AI3001</t>
+          <t>AI4009</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Knowledge Rep. and Reasoning</t>
+          <t>Generative AI</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1877,32 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>26-10-30</t>
+          <t>26-10-29</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>SS2012</t>
+          <t>AI4009</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Technical and Business Writing</t>
+          <t>Generative AI</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>26-10-30</t>
+          <t>26-10-29</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -1922,17 +1922,17 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>SS2012</t>
+          <t>AI3001</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Technical and Business Writing</t>
+          <t>Knowledge Rep. and Reasoning</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(SE) (A,B, C)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2022,27 +2022,27 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>SS2012</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Technical and Business Writing</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -2057,27 +2057,27 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>SS2012</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Technical and Business Writing</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -2197,27 +2197,27 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>CS3004</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Software Design and Analysis</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>EE3009</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Computer Architecture</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -2267,22 +2267,22 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>SS1022</t>
+          <t>CS3004</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
+          <t>Software Design and Analysis</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -2302,27 +2302,27 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>SS1022</t>
+          <t>EE3009</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
+          <t>Computer Architecture</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -2337,27 +2337,27 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>SS2012</t>
+          <t>CS4049</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Technical and Business Writing</t>
+          <t>Blockchain and Cryptocurrency</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(CY) (A,B)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B, C)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -2477,27 +2477,27 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>SS2012</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Technical and Business Writing</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -2652,27 +2652,27 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>DS3001</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Data Analysis and Visualization</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -2687,27 +2687,27 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>SS1015</t>
+          <t>DS3001</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Pakistan Studies</t>
+          <t>Data Analysis and Visualization</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -2792,27 +2792,27 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>CS4049</t>
+          <t>SS1015</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Blockchain and Cryptocurrency</t>
+          <t>Pakistan Studies</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -2827,27 +2827,27 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>CS3002</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Technical and Business Writing</t>
+          <t>Information Security</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -2897,27 +2897,27 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Technical and Business Writing</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -3072,27 +3072,27 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>CS4046</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Game Design and Development</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -3107,27 +3107,27 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>SS1015</t>
+          <t>CS4046</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Pakistan Studies</t>
+          <t>Game Design and Development</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -3212,27 +3212,27 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>CS3002</t>
+          <t>SS1015</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Information Security</t>
+          <t>Pakistan Studies</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3247,22 +3247,22 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>AI4015</t>
+          <t>CS3002</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Agentic Artificial Intelligence</t>
+          <t>Information Security</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(CS) (A,B,C,D,,E,F,G)</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -3282,22 +3282,22 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>AI4015</t>
+          <t>CS3002</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Agentic Artificial Intelligence</t>
+          <t>Information Security</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(SE) (A,B)</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -3352,27 +3352,27 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>CL1002</t>
+          <t>AI4015</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals Lab</t>
+          <t>Agentic Artificial Intelligence</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3387,27 +3387,27 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>CL1002</t>
+          <t>AI4015</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals Lab</t>
+          <t>Agentic Artificial Intelligence</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>CS3002</t>
+          <t>CS4059</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Information Security</t>
+          <t>Fundamentals of Computer Vision</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,,E,F,G)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -3492,22 +3492,22 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>CS3002</t>
+          <t>CY3002</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Information Security</t>
+          <t>Vulnerability Assessment and Reverse Engg</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B)</t>
+          <t>BS(CY)</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>CY3002</t>
+          <t>CY3003</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Vulnerability Assessment and Reverse Engg</t>
+          <t>Information Assurance</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3562,27 +3562,27 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>CY3003</t>
+          <t>CL1002</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Information Assurance</t>
+          <t>Programming Fundamentals Lab</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>BS(CY)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -3667,27 +3667,27 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>CL1002</t>
+          <t>CS1004</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals Lab</t>
+          <t>Object Oriented Programming</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3702,27 +3702,27 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>CS4059</t>
+          <t>CS1004</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Computer Vision</t>
+          <t>Object Oriented Programming</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(SE) (A)</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D)</t>
+          <t>BS(AI) (A)</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -3772,27 +3772,27 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>CS1004</t>
+          <t>CL3001</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Object Oriented Programming</t>
+          <t>Computer Networks Lab</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -3807,27 +3807,27 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>CS1004</t>
+          <t>CL1002</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Object Oriented Programming</t>
+          <t>Programming Fundamentals Lab</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -3837,27 +3837,27 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>26-10-31</t>
+          <t>26-10-30</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>CL1002</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>Programming Fundamentals Lab</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E)</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -4017,27 +4017,27 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>AI3002</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -4052,27 +4052,27 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>SS1007</t>
+          <t>AI3002</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Islamic Studies/Ethics</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B, C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(AI) (A,B, C)</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -4157,27 +4157,27 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>CS2001</t>
+          <t>SS1007</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Islamic Studies/Ethics</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -4332,27 +4332,27 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>CS2009</t>
+          <t>CS2001</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Design and Analysis of Algorithms</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B,C)</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -4472,27 +4472,27 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>CS1005</t>
+          <t>CS2009</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Discrete Structures</t>
+          <t>Design and Analysis of Algorithms</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -4507,27 +4507,27 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>CS1005</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>Discrete Structures</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(CS) (A,B)</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E)</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>CS4001</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Professional Practices in IT</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,,E,F,G,H)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B)</t>
+          <t>BS(CS) (A,B,C,D,,E,F,G,H)</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -4752,27 +4752,27 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>SS1007</t>
+          <t>CS4001</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Islamic Studies/Ethics</t>
+          <t>Professional Practices in IT</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
+          <t>BS(CY) (A,B)</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B, C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,Z)</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(AI) (A,B, C)</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -4857,27 +4857,27 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>CS2001</t>
+          <t>SS1007</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Islamic Studies/Ethics</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -5032,27 +5032,27 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>CS2009</t>
+          <t>CS2001</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Design and Analysis of Algorithms</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B,C)</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -5172,27 +5172,27 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>CS4039</t>
+          <t>CS2009</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Software for Mobile Devices</t>
+          <t>Design and Analysis of Algorithms</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -5242,27 +5242,27 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>CS4039</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>Software for Mobile Devices</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E)</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -5417,27 +5417,27 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>AI4012</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Multiagent Systems and Game Theory</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>CS2001</t>
+          <t>AI4012</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Data Structures</t>
+          <t>Multiagent Systems and Game Theory</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -5662,27 +5662,27 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>SS1026</t>
+          <t>CS2001</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Arts Humanities and Technology</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -5732,27 +5732,27 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>CS4044</t>
+          <t>SS1026</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Software Project Management</t>
+          <t>Arts Humanities and Technology</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -5767,27 +5767,27 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>CS2005</t>
+          <t>CS4044</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Database Systems</t>
+          <t>Fundamentals of Software Project Management</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -5802,27 +5802,27 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>CY2004</t>
+          <t>CS2005</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>Database Systems</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>BS(CY)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -5837,27 +5837,27 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>CS4085</t>
+          <t>DS2003</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Advanced Statistics</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -5872,27 +5872,27 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>SS1026</t>
+          <t>CS4085</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Arts Humanities and Technology</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(SE) (A,B, C,D,E,F)</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -5942,27 +5942,27 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>CY4054</t>
+          <t>SS1026</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Blockchain Technologies and Applications</t>
+          <t>Arts Humanities and Technology</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -5977,27 +5977,27 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>DS2003</t>
+          <t>CY4054</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Advanced Statistics</t>
+          <t>Blockchain Technologies and Applications</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -6012,27 +6012,27 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>SE3005</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Software Construction and Development</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J, Z)</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6047,27 +6047,27 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>CS4063</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6082,17 +6082,17 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>CL1002</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals Lab</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6117,27 +6117,27 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>CL1002</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals Lab</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6152,27 +6152,27 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>CS4032</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Web Programming</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>BS(CY)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6187,27 +6187,27 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>CL1002</t>
+          <t>SE3005</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals Lab</t>
+          <t>Software Construction and Development</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E,F)</t>
+          <t>BS(SE) (A,B,C)</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -6217,32 +6217,32 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>26-11-02</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>CS4063</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Natural Language Processing</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(SE) (A,B)</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -6252,32 +6252,32 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>26-11-02</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>CS4032</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Web Programming</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(CY)</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -6287,32 +6287,32 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>26-11-02</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J, Z)</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6322,32 +6322,32 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>26-11-02</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6357,32 +6357,32 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>26-11-02</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>26-11-02</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -6402,22 +6402,22 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>AL3002</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Lab</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6427,27 +6427,27 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>26-11-02</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -6467,27 +6467,27 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6502,27 +6502,27 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6537,27 +6537,27 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6572,27 +6572,27 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6607,27 +6607,27 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>CS4045</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Deep Learning for Perception</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -6642,22 +6642,22 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>CS3001</t>
+          <t>AL3002</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Machine Learning Lab</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -6677,27 +6677,27 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>CS3001</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6712,22 +6712,22 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>DS2001</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Data Science</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -6747,27 +6747,27 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6817,27 +6817,27 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6852,27 +6852,27 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>CS4045</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Deep Learning for Perception</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>MT1003</t>
+          <t>CS3001</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Calculus and Analytical Geometry</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C,D)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G)</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -6922,17 +6922,17 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>AL3002</t>
+          <t>CS3001</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Lab</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -6957,22 +6957,22 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>DS2001</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Introduction to Data Science</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -6992,27 +6992,27 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C,D)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -7027,27 +7027,27 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -7062,27 +7062,27 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -7097,27 +7097,27 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -7132,27 +7132,27 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>AI4019</t>
+          <t>MT1003</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Edge Computing and Intelligent Systems</t>
+          <t>Calculus and Analytical Geometry</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B)</t>
+          <t>BS(CY) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -7167,27 +7167,27 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>AI4019</t>
+          <t>AL3002</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>Edge Computing and Intelligent Systems</t>
+          <t>Machine Learning Lab</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -7202,27 +7202,27 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>CS3001</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>BS(DS)</t>
+          <t>BS(CS) (A,B,C,D,E,F,G,H,J)</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -7237,22 +7237,22 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>SE1001</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Software Engineering</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(SE) (A,B,C,D)</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -7277,22 +7277,22 @@
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>SE4033</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>Formal Methods in Software Engineering</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>BS(SE)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -7307,27 +7307,27 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>CL1000</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Information and Communication Technology</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS) (A,B)</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -7342,27 +7342,27 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>CL1000</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Information and Communication Technology</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -7382,22 +7382,22 @@
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>CL1000</t>
+          <t>AI4019</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Information and Communication Technology</t>
+          <t>Edge Computing and Intelligent Systems</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E)</t>
+          <t>BS(AI) (A,B)</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7412,22 +7412,22 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>CY4048</t>
+          <t>AI4019</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Security Operations and Administration</t>
+          <t>Edge Computing and Intelligent Systems</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B)</t>
+          <t>BS(DS) (A)</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -7452,17 +7452,17 @@
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>CY4048</t>
+          <t>CS3001</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Security Operations and Administration</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -7487,17 +7487,17 @@
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>AI2001</t>
+          <t>SE1001</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Programming for AI</t>
+          <t>Introduction to Software Engineering</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -7517,27 +7517,27 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>CS2006</t>
+          <t>CL3001</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Operating Systems</t>
+          <t>Computer Networks Lab</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>BS(CY) (A,B,C)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7552,27 +7552,27 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>CS2006</t>
+          <t>SE4033</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Operating Systems</t>
+          <t>Formal Methods in Software Engineering</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A)</t>
+          <t>BS(SE)</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7587,27 +7587,27 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>CS4095</t>
+          <t>CL1000</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Embedded Control of Robotics</t>
+          <t>Introduction to Information and Communication Technology</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(AI) (A,B,C)</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>BS(AI) (A,B,C)</t>
+          <t>BS(DS) (A,B,C)</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>BS(DS) (A,B,C)</t>
+          <t>BS(SE) (A,B, C,D,E)</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -7692,27 +7692,27 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>CL1000</t>
+          <t>CY4048</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Information and Communication Technology</t>
+          <t>Security Operations and Administration</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B, C,D,E)</t>
+          <t>BS(CY) (A,B)</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7732,17 +7732,17 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>AI4013</t>
+          <t>CY4048</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>AI Product Development</t>
+          <t>Security Operations and Administration</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>BS(AI)</t>
+          <t>BS(CY) (A)</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -7767,22 +7767,22 @@
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>CS3006</t>
+          <t>AI2001</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>Parallel and Distributed Computing</t>
+          <t>Programming for AI</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D)</t>
+          <t>BS(AI)</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -7797,27 +7797,27 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>CS3006</t>
+          <t>CS2006</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>Parallel and Distributed Computing</t>
+          <t>Operating Systems</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B)</t>
+          <t>BS(CY) (A,B,C)</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -7837,22 +7837,22 @@
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>CS3012</t>
+          <t>CS2006</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Data Visualization</t>
+          <t>Operating Systems</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>BS(CS)</t>
+          <t>BS(DS) (A)</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -7867,27 +7867,27 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>CL1002</t>
+          <t>CL3001</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Computer Networks Lab</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+          <t>BS(DS)</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7902,27 +7902,27 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>SE3002</t>
+          <t>CS4095</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>Software Quality Engineering</t>
+          <t>Embedded Control of Robotics</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>BS(SE) (A,B,C)</t>
+          <t>BS(CS)</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -7937,27 +7937,377 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
+          <t>01:00 to 02:00 PM</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>CL1000</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>Introduction to Information and Communication Technology</t>
+        </is>
+      </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>BS(AI) (A,B,C)</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>01:00 to 02:00 PM</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>CL1000</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>Introduction to Information and Communication Technology</t>
+        </is>
+      </c>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>BS(DS) (A,B,C)</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>01:00 to 02:00 PM</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>CL1000</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>Introduction to Information and Communication Technology</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>BS(SE) (A,B, C,D,E)</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
           <t>02:30 to 03:30 PM</t>
         </is>
       </c>
-      <c r="D216" s="3" t="inlineStr">
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>AI4013</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>AI Product Development</t>
+        </is>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>BS(AI)</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>03:40 to 04:40 PM</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>CY2004</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>Cyber Security</t>
+        </is>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>BS(CY)</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>9:00 to 10:00 AM</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>CS3012</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>Fundamentals of Data Visualization</t>
+        </is>
+      </c>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>BS(CS)</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>02:30 to 03:30 PM</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t>CL1002</t>
         </is>
       </c>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>Programming Fundamentals</t>
-        </is>
-      </c>
-      <c r="F216" s="4" t="inlineStr">
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>Programming Fundamentals  Lab</t>
+        </is>
+      </c>
+      <c r="F222" s="4" t="inlineStr">
         <is>
           <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
         </is>
       </c>
-      <c r="G216" s="3" t="inlineStr">
+      <c r="G222" s="3" t="inlineStr">
         <is>
           <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>03:40 to 04:40 PM</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>CS3006</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>Parallel and Distributed Computing</t>
+        </is>
+      </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>BS(CS) (A,B,C,D)</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>03:40 to 04:40 PM</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>CS3006</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>Parallel and Distributed Computing</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>BS(SE) (A,B)</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>02:30 to 03:30 PM</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>CL1002</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>Programming Fundamentals  Lab</t>
+        </is>
+      </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>BS(CS) (A,B,C,D,E,F,G,H)</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>26-11-02</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>03:40 to 04:40 PM</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>SE3002</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>Software Quality Engineering</t>
+        </is>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>BS(SE) (A,B,C)</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -7975,7 +8325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9167,22 +9517,22 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>SS2042</t>
+          <t>MG2011</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Community Service</t>
+          <t>Environmental Science and Sustainability for Business</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -9197,27 +9547,27 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>MG1011</t>
+          <t>MG2011</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Business Mathematics</t>
+          <t>Environmental Science and Sustainability for Business</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9597,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -9282,7 +9632,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -9302,27 +9652,27 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>MG4011</t>
+          <t>MG1011</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Entrepreneurship</t>
+          <t>Business Mathematics</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -9337,22 +9687,22 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>MG2003</t>
+          <t>MG4011</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Consumer Behaviour</t>
+          <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -9377,22 +9727,22 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>MG2003</t>
+          <t>MG1001</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Behaviour</t>
+          <t>Fundamentals of Management</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -9407,27 +9757,27 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>MG4523</t>
+          <t>MG1001</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Conflict Resolution and Negotiation Skills</t>
+          <t>Fundamentals of Management</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -9442,17 +9792,17 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>5:00 to 6:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>BA4006</t>
+          <t>MG2003</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Contextual Marketing and Product Analytics</t>
+          <t>Consumer Behaviour</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -9462,7 +9812,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -9477,27 +9827,27 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>SS2043</t>
+          <t>MG2003</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Civics and Community Engagement</t>
+          <t>Consumer Behaviour</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -9512,27 +9862,27 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>5:00 to 6:00 PM</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>SS2043</t>
+          <t>BA4006</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Civics and Community Engagement</t>
+          <t>Contextual Marketing and Product Analytics</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -9547,17 +9897,17 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>MG1011</t>
+          <t>MG2011</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Business Mathematics</t>
+          <t>Environmental Science and Sustainability for Business</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -9567,7 +9917,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -9582,27 +9932,27 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>MG1011</t>
+          <t>MG2011</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Business Mathematics</t>
+          <t>Environmental Science and Sustainability for Business</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -9632,7 +9982,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -9652,27 +10002,27 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>MG4011</t>
+          <t>MG1011</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Entrepreneurship</t>
+          <t>Business Mathematics</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -9687,17 +10037,17 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>MG4011</t>
+          <t>MG1011</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Entrepreneurship</t>
+          <t>Business Mathematics</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -9707,7 +10057,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -9722,27 +10072,27 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>SS2006</t>
+          <t>MG4011</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Macro Economics</t>
+          <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -9757,27 +10107,27 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>MG2011</t>
+          <t>MG4011</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Environmental Science and Sustainability for Business</t>
+          <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -9792,17 +10142,17 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>MG2011</t>
+          <t>MG1001</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Environmental Science and Sustainability for Business</t>
+          <t>Fundamentals of Management</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -9812,7 +10162,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -9827,27 +10177,27 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>MT1002</t>
+          <t>MG1001</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Business Math – I</t>
+          <t>Fundamentals of Management</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -9862,22 +10212,22 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>MG2001</t>
+          <t>MT2004</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Organizational Behaviour</t>
+          <t>Business Math – II</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -9897,27 +10247,27 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>MG3002</t>
+          <t>AF3006</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>Financing New Ventures</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -9932,22 +10282,22 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>MT2004</t>
+          <t>MT1002</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Business Math – II</t>
+          <t>Business Math – I</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -9967,22 +10317,22 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>MG2011</t>
+          <t>MG2001</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Environmental Science and Sustainability for Business</t>
+          <t>Organizational Behaviour</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -10002,27 +10352,27 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>MG2011</t>
+          <t>SS2006</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Environmental Science and Sustainability for Business</t>
+          <t>Macro Economics</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -10037,22 +10387,22 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>MG4062</t>
+          <t>MG1004</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Brand Management</t>
+          <t>Business Calculus II</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -10072,27 +10422,27 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>AF2001</t>
+          <t>AF4017</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Corporate Accounting – I</t>
+          <t>Digital Assets and Cryptocurrencies; Conventiontional and Shariah Persepectives</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -10107,27 +10457,27 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>MG1001</t>
+          <t>AF2001</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Management</t>
+          <t>Corporate Accounting – I</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10147,22 +10497,22 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>MG1001</t>
+          <t>MG3002</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Management</t>
+          <t>Business Law</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -10177,22 +10527,22 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>5:00 to 6:00 PM</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>MG1004</t>
+          <t>MG4066</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Business Calculus II</t>
+          <t>Managing Virtual Global Teams</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -10207,32 +10557,32 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>26-10-30</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>5:00 to 6:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>MG4066</t>
+          <t>SS1016</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Managing Virtual Global Teams</t>
+          <t>English - I</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10592,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>26-10-30</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -10252,12 +10602,12 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>AF3006</t>
+          <t>SS1016</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Financing New Ventures</t>
+          <t>English - I</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -10267,7 +10617,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -10277,32 +10627,32 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>26-10-30</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>AF4017</t>
+          <t>SS1016</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Digital Assets and Cryptocurrencies; Conventiontional and Shariah Persepectives</t>
+          <t>English - I</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10682,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -10352,27 +10702,27 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>SS1016</t>
+          <t>BA3002</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>English - I</t>
+          <t>Business Data and Text Mining</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -10387,27 +10737,27 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>SS1016</t>
+          <t>MG2009</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>English - I</t>
+          <t>Data Analysis for Business II</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10422,27 +10772,27 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>SS1016</t>
+          <t>MG2009</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>English - I</t>
+          <t>Data Analysis for Business II</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10457,27 +10807,27 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>BA3002</t>
+          <t>MG2009</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Business Data and Text Mining</t>
+          <t>Data Analysis for Business II</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10492,17 +10842,17 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>MG2009</t>
+          <t>SS1015</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Data Analysis for Business II</t>
+          <t>Pakistan Studies</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -10512,7 +10862,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -10527,17 +10877,17 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>MG2009</t>
+          <t>SS1015</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Data Analysis for Business II</t>
+          <t>Pakistan Studies</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -10547,7 +10897,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -10562,22 +10912,22 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>MG2009</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Data Analysis for Business II</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -10597,27 +10947,27 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>SS1015</t>
+          <t>SS1013</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Pakistan Studies</t>
+          <t>Ideology and Constitution of Pakistan</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10632,17 +10982,17 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>SS1015</t>
+          <t>CS2003</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Pakistan Studies</t>
+          <t>Data Structures and Business Applications</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -10652,7 +11002,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -10667,27 +11017,27 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>SS1016</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>English - I</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -10702,27 +11052,27 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>SS1013</t>
+          <t>SS1016</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Ideology and Constitution of Pakistan</t>
+          <t>English - I</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -10737,17 +11087,17 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>CS2003</t>
+          <t>SS1016</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Data Structures and Business Applications</t>
+          <t>English - I</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -10757,7 +11107,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -10787,7 +11137,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -10807,17 +11157,17 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>SS1016</t>
+          <t>CY4053</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>English - I</t>
+          <t>Cybersecurity for FinTech</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -10827,7 +11177,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -10842,27 +11192,27 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>SS1016</t>
+          <t>MG2009</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>English - I</t>
+          <t>Data Analysis for Business II</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10877,27 +11227,27 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>SS1016</t>
+          <t>MG2009</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>English - I</t>
+          <t>Data Analysis for Business II</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10912,27 +11262,27 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>CY4053</t>
+          <t>MG2009</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity for FinTech</t>
+          <t>Data Analysis for Business II</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10947,27 +11297,27 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>MG2009</t>
+          <t>CS3011</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Data Analysis for Business II</t>
+          <t>Enterprise Information System</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -10982,27 +11332,27 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>MG2009</t>
+          <t>MG3006</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Data Analysis for Business II</t>
+          <t>Operations Management</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11017,27 +11367,27 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>MG2009</t>
+          <t>CS3003</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Data Analysis for Business II</t>
+          <t>Management Information Systems</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11052,17 +11402,17 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>CS3011</t>
+          <t>CS2012</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Information System</t>
+          <t>Introduction to Object-Oriented Programming</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -11072,7 +11422,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -11087,22 +11437,22 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>MG3006</t>
+          <t>CS3017</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Operations Management</t>
+          <t>Enterprise Systems and Applications</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -11122,27 +11472,27 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>CS2016</t>
+          <t>AF4005</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Programming for Business</t>
+          <t>Audit and Assurance</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -11157,27 +11507,27 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>CS3017</t>
+          <t>MG4523</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Systems and Applications</t>
+          <t>Conflict Resolution and Negotiation Skills</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -11192,22 +11542,22 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>AF4005</t>
+          <t>MG4062</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Audit and Assurance</t>
+          <t>Brand Management</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -11227,27 +11577,27 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>CS3003</t>
+          <t>AF3003</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Management Information Systems</t>
+          <t>Financial Institutions and Markets</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A,B)</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -11262,22 +11612,22 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>CS2012</t>
+          <t>MG2010</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Introduction to Object-Oriented Programming</t>
+          <t>Business Communication</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -11292,32 +11642,32 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>26-10-31</t>
+          <t>26-11-02</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>AF3003</t>
+          <t>CS1001</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Financial Institutions and Markets</t>
+          <t>IT in Business</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -11327,32 +11677,32 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>26-10-31</t>
+          <t>26-11-02</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>MG2010</t>
+          <t>CS1001</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Business Communication</t>
+          <t>IT in Business</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -11362,22 +11712,22 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>26-10-31</t>
+          <t>26-11-02</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>MG3014</t>
+          <t>CS1001</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Advanced Business Communications</t>
+          <t>IT in Business</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -11387,7 +11737,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -11402,27 +11752,27 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>CS1001</t>
+          <t>MG4522</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>IT in Business</t>
+          <t>Islamic Banking and Finance</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -11437,27 +11787,27 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>CS1001</t>
+          <t>MG2012</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>IT in Business</t>
+          <t>Business Economics</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -11472,27 +11822,27 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>CS1001</t>
+          <t>MG2012</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>IT in Business</t>
+          <t>Business Economics</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -11507,27 +11857,27 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>MG4522</t>
+          <t>MG2012</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Islamic Banking and Finance</t>
+          <t>Business Economics</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11907,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -11577,27 +11927,27 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>MG2012</t>
+          <t>MG4045</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Business Economics</t>
+          <t>Strategic Business Reporting</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -11612,17 +11962,17 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>MG2012</t>
+          <t>CS2016</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Business Economics</t>
+          <t>Programming for Business</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -11647,27 +11997,27 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>MG2012</t>
+          <t>MG3003</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Business Economics</t>
+          <t>Basic Econometrics</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11682,27 +12032,27 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>MG4045</t>
+          <t>MG3003</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Strategic Business Reporting</t>
+          <t>Basic Econometrics</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11717,27 +12067,27 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>MG1002</t>
+          <t>MG3003</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Marketing Management</t>
+          <t>Basic Econometrics</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -11752,17 +12102,17 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>MG1002</t>
+          <t>CS1001</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Marketing Management</t>
+          <t>IT in Business</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -11787,27 +12137,27 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>MG3003</t>
+          <t>CS1001</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Basic Econometrics</t>
+          <t>IT in Business</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -11822,27 +12172,27 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>MG3003</t>
+          <t>CS1001</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Basic Econometrics</t>
+          <t>IT in Business</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -11857,22 +12207,22 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>MG3003</t>
+          <t>SS2002</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Basic Econometrics</t>
+          <t>Micro Economics</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -11892,27 +12242,27 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>CS1001</t>
+          <t>MG2012</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>IT in Business</t>
+          <t>Business Economics</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -11927,27 +12277,27 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>CS1001</t>
+          <t>MG2012</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>IT in Business</t>
+          <t>Business Economics</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -11962,27 +12312,27 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>CS1001</t>
+          <t>MG2012</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>IT in Business</t>
+          <t>Business Economics</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -11997,27 +12347,27 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>SS2002</t>
+          <t>MG2012</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Micro Economics</t>
+          <t>Business Economics</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>BBA (A)</t>
+          <t>BBA (A,B,C,D)</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -12032,17 +12382,17 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>MG2012</t>
+          <t>AF2005</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Business Economics</t>
+          <t>Cost and Management Accounting</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -12052,7 +12402,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -12067,27 +12417,27 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>MG2012</t>
+          <t>SS2018</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Business Economics</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -12102,27 +12452,27 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>MG2012</t>
+          <t>MG3003</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Business Economics</t>
+          <t>Basic Econometrics</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -12137,27 +12487,27 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>MG2012</t>
+          <t>MG3003</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Business Economics</t>
+          <t>Basic Econometrics</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C,D)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -12172,22 +12522,22 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>AF2005</t>
+          <t>MG3003</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Cost and Management Accounting</t>
+          <t>Basic Econometrics</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -12207,17 +12557,17 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>SS2018</t>
+          <t>MG3014</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Advanced Business Communications</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -12227,7 +12577,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -12242,22 +12592,22 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>MG3003</t>
+          <t>SS2018</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Basic Econometrics</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>BS(AF)</t>
+          <t>BBA (A)</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -12282,22 +12632,22 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>MG3003</t>
+          <t>MG4003</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Basic Econometrics</t>
+          <t>Strategic Management</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BBA (A,B)</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -12312,17 +12662,17 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>MG3003</t>
+          <t>BA4007</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Basic Econometrics</t>
+          <t>Empowering Organizations with Analytics and Data Visualization</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -12332,7 +12682,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -12347,22 +12697,22 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>BA4007</t>
+          <t>AF4011</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Empowering Organizations with Analytics and Data Visualization</t>
+          <t>Investment and Portfolio Analytics</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -12382,22 +12732,22 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>AF4011</t>
+          <t>MG4521</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Investment and Portfolio Analytics</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>BS(FT)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -12422,12 +12772,12 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>SS2018</t>
+          <t>MG4521</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -12437,7 +12787,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -12452,27 +12802,27 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>MG4003</t>
+          <t>MG3004</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Strategic Management</t>
+          <t>Human Resource Mgmt.</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B)</t>
+          <t>BS(BA)</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12852,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BBA (A,B,C)</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -12527,22 +12877,22 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>MG3004</t>
+          <t>MG1002</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Human Resource Mgmt.</t>
+          <t>Marketing Management</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>BBA (A,B,C)</t>
+          <t>BS(AF)</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -12557,62 +12907,27 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>MG4521</t>
+          <t>MG1002</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>Marketing Management</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>BS(BA)</t>
+          <t>BS(FT)</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="n">
-        <v>131</v>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>26-11-02</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>02:30 to 03:30 PM</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>MG4521</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>Digital Marketing</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>BBA (A)</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12912,22 +13227,22 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>SS2043</t>
+          <t>EE3006</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Civics and Community Engagement</t>
+          <t>Embedded Systems</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A,B)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -13077,32 +13392,32 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>26-10-29</t>
+          <t>26-10-30</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>EE3006</t>
+          <t>NS1002</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Embedded Systems</t>
+          <t>Physics for Engineers</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13447,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -13152,27 +13467,27 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>NS1002</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Physics for Engineers</t>
+          <t>Technical and Business Writing</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -13187,27 +13502,27 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>CY4054</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Technical and Business Writing</t>
+          <t>Blockchain Technologies and Applications</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13222,27 +13537,27 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>CY4054</t>
+          <t>EE1004</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Blockchain Technologies and Applications</t>
+          <t>Electronic Devices and Circuits</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(CE) (A,B)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13257,27 +13572,27 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>EE1004</t>
+          <t>EE3002</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Electronic Devices and Circuits</t>
+          <t>µP Interfacing and Programming</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A,B)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -13292,27 +13607,27 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>EE3002</t>
+          <t>NS1002</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>µP Interfacing and Programming</t>
+          <t>Physics for Engineers</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13657,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -13362,27 +13677,27 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>NS1002</t>
+          <t>EE2004</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Physics for Engineers</t>
+          <t>Electrical Network Analysis</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13397,27 +13712,27 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>EE2004</t>
+          <t>ME2002</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Electrical Network Analysis</t>
+          <t>Applied Thermodynamics</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -13432,27 +13747,27 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>ME2002</t>
+          <t>CS2021</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Applied Thermodynamics</t>
+          <t>Object Oriented Data Structures</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13467,17 +13782,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>CS2021</t>
+          <t>EE3012</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Object Oriented Data Structures</t>
+          <t>µP Interfacing and Programming</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -13487,7 +13802,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13502,27 +13817,27 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>EE3012</t>
+          <t>CS1002</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>µP Interfacing and Programming</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13542,17 +13857,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>CS1002</t>
+          <t>CS1011</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Programming Fundamentals</t>
+          <t>Programming for Engineers</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -13567,27 +13882,27 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>26-10-30</t>
+          <t>26-10-31</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>CS1011</t>
+          <t>MT2013</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Programming for Engineers</t>
+          <t>Complex Variables and Transforms</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(CE) (A,B)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -13622,7 +13937,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A,B)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -13642,27 +13957,27 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>MT2013</t>
+          <t>EE2012</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Complex Variables and Transforms</t>
+          <t>Computer Organization and Architecture</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13677,17 +13992,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>EE2012</t>
+          <t>SS1005</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Computer Organization and Architecture</t>
+          <t>English Language</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -13697,7 +14012,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13727,7 +14042,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -13747,27 +14062,27 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>SS1005</t>
+          <t>EE3005</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>English Language</t>
+          <t>Electromagnetic Theory</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13782,27 +14097,27 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>EE3005</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Electromagnetic Theory</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A,B)</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13817,27 +14132,27 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT2011</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Complex Variables and Transforms</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A,B)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13852,27 +14167,27 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>MT2011</t>
+          <t>NS1007</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Complex Variables and Transforms</t>
+          <t>Applied Physics</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -13887,27 +14202,27 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>NS1007</t>
+          <t>SS1005</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Applied Physics</t>
+          <t>English Language</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -13937,7 +14252,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -13957,27 +14272,27 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>SS1005</t>
+          <t>EE3005</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>English Language</t>
+          <t>Electromagnetic Theory</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -13992,27 +14307,27 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>EE3005</t>
+          <t>MT1004</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Electromagnetic Theory</t>
+          <t>Linear Algebra</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -14027,27 +14342,27 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>MT1004</t>
+          <t>MT2003</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Linear Algebra</t>
+          <t>Complex Variables and Transforms</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(EE) (B,C)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -14062,22 +14377,22 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>MT2003</t>
+          <t>EE2031</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Complex Variables and Transforms</t>
+          <t>Instrumentation and Measurements</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (B,C)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -14097,17 +14412,17 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>EE2031</t>
+          <t>CS2011</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Instrumentation and Measurements</t>
+          <t>Fundamentals of Databases</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -14127,32 +14442,32 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>26-10-31</t>
+          <t>26-11-02</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>CS2011</t>
+          <t>CS1009</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Fundamentals of Databases</t>
+          <t>Applications of Information Communication Technologies</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14497,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -14202,27 +14517,27 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>CS1009</t>
+          <t>CS1005</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Applications of Information Communication Technologies</t>
+          <t>Discrete Structures</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A,B)</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -14237,27 +14552,27 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>10:20 to 11:20 AM</t>
+          <t>11:40 to 12:40 PM</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>CS1005</t>
+          <t>ME2001</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Discrete Structures</t>
+          <t>Basic Mechanical Engineering</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A,B)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -14272,17 +14587,17 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>01:00 to 02:00 PM</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>ME2001</t>
+          <t>SS1022</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Basic Mechanical Engineering</t>
+          <t>Understanding of Holy Quran I/Introduction to Major World Religions II</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -14292,7 +14607,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -14307,17 +14622,17 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>01:00 to 02:00 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>SS1022</t>
+          <t>EE3003</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Understanding of Holy Quran I/Introduction to Major World Religions I</t>
+          <t>Analogue and Digital Communication</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -14327,7 +14642,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -14342,27 +14657,27 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>02:30 to 03:30 PM</t>
+          <t>03:40 to 04:40 PM</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>EE3003</t>
+          <t>SS1015</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Analogue and Digital Communication</t>
+          <t>Pakistan Studies</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14707,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -14412,22 +14727,22 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>03:40 to 04:40 PM</t>
+          <t>9:00 to 10:00 AM</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>SS1015</t>
+          <t>CS1009</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Pakistan Studies</t>
+          <t>Applications of Information Communication Technologies</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -14462,7 +14777,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B,C)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -14482,27 +14797,27 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>9:00 to 10:00 AM</t>
+          <t>10:20 to 11:20 AM</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>CS1009</t>
+          <t>EE3031</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Applications of Information Communication Technologies</t>
+          <t>Digital Signal Processing</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B,C)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -14522,22 +14837,22 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>EE3031</t>
+          <t>AI4003</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Digital Signal Processing</t>
+          <t>Applied Machine Learning</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A,B)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -14657,27 +14972,27 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>11:40 to 12:40 PM</t>
+          <t>02:30 to 03:30 PM</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>AI4003</t>
+          <t>CS2008</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Applied Machine Learning</t>
+          <t>Numerical Computing</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>BS(EE) (A,B)</t>
+          <t>BS(CE) (A)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -14697,55 +15012,20 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>CS2008</t>
+          <t>EE1001</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Numerical Computing</t>
+          <t>Linear Circuit Analysis</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>BS(CE) (A)</t>
+          <t>BS(EE) (A)</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>26-11-02</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>02:30 to 03:30 PM</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>EE1001</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Linear Circuit Analysis</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>BS(EE) (A)</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
